--- a/data/trans_orig/IP2904-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2904-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38131</t>
+          <t>38413</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53612</t>
+          <t>53416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31372</t>
+          <t>32116</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46403</t>
+          <t>46380</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74643</t>
+          <t>73829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95898</t>
+          <t>95341</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>17006</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23105</t>
+          <t>22895</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>20529</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36449</t>
+          <t>37131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23248</t>
+          <t>23563</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37467</t>
+          <t>38489</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>21831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34961</t>
+          <t>35074</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48478</t>
+          <t>49073</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68442</t>
+          <t>68363</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,98%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>162386</t>
+          <t>161777</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>192989</t>
+          <t>193818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>196095</t>
+          <t>196014</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>230969</t>
+          <t>230662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>370457</t>
+          <t>370081</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>415101</t>
+          <t>415368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,53%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73353</t>
+          <t>71817</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99324</t>
+          <t>98149</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>105354</t>
+          <t>106261</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>135019</t>
+          <t>134055</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>186005</t>
+          <t>186258</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>225372</t>
+          <t>226863</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120347</t>
+          <t>120178</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149544</t>
+          <t>149569</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109475</t>
+          <t>110739</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139822</t>
+          <t>140622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>239165</t>
+          <t>236738</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>280665</t>
+          <t>282481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63310</t>
+          <t>62642</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>83740</t>
+          <t>83296</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46299</t>
+          <t>46449</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64797</t>
+          <t>66181</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115795</t>
+          <t>114280</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>144600</t>
+          <t>142370</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41122</t>
+          <t>40852</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60155</t>
+          <t>59137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38974</t>
+          <t>38805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56216</t>
+          <t>56534</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85233</t>
+          <t>84981</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111190</t>
+          <t>112715</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34153</t>
+          <t>33632</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51362</t>
+          <t>51053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40728</t>
+          <t>39731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58314</t>
+          <t>58297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76860</t>
+          <t>78228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102651</t>
+          <t>102493</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>276696</t>
+          <t>278296</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>317608</t>
+          <t>317733</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>287591</t>
+          <t>289266</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>326996</t>
+          <t>331969</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>576850</t>
+          <t>577970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>635191</t>
+          <t>633876</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,18%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129260</t>
+          <t>130223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164220</t>
+          <t>164861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>167548</t>
+          <t>163434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203196</t>
+          <t>202107</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>305542</t>
+          <t>307798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>356348</t>
+          <t>356171</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187456</t>
+          <t>187317</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>225634</t>
+          <t>225327</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>183503</t>
+          <t>179007</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>222158</t>
+          <t>219384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>381913</t>
+          <t>381391</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>434354</t>
+          <t>433731</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37911</t>
+          <t>38699</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53549</t>
+          <t>53944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30786</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45919</t>
+          <t>46463</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74202</t>
+          <t>73343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94475</t>
+          <t>95230</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>55,34%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28338</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15041</t>
+          <t>14686</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>28052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33262</t>
+          <t>32841</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51649</t>
+          <t>52192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16476</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29210</t>
+          <t>29998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17472</t>
+          <t>16979</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31201</t>
+          <t>31143</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36126</t>
+          <t>36393</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55149</t>
+          <t>56372</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197031</t>
+          <t>196420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230879</t>
+          <t>230014</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>226219</t>
+          <t>227373</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>261697</t>
+          <t>262368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>433689</t>
+          <t>432235</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>483546</t>
+          <t>484787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88691</t>
+          <t>89463</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>119391</t>
+          <t>121229</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101414</t>
+          <t>101499</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>130598</t>
+          <t>131222</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>200042</t>
+          <t>198971</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>242343</t>
+          <t>240981</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104816</t>
+          <t>103808</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135359</t>
+          <t>132901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102454</t>
+          <t>101530</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132760</t>
+          <t>132088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>213801</t>
+          <t>214308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256945</t>
+          <t>256668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57525</t>
+          <t>58904</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78311</t>
+          <t>79779</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61121</t>
+          <t>62337</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81717</t>
+          <t>83259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>126934</t>
+          <t>126320</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>156560</t>
+          <t>155464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,25%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35900</t>
+          <t>34519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54350</t>
+          <t>52742</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43738</t>
+          <t>44440</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65208</t>
+          <t>64398</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85423</t>
+          <t>84504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113732</t>
+          <t>112140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38211</t>
+          <t>37334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56423</t>
+          <t>56994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27323</t>
+          <t>27376</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45493</t>
+          <t>45366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70638</t>
+          <t>69555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96837</t>
+          <t>95255</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>303964</t>
+          <t>307035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>349135</t>
+          <t>350857</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>332973</t>
+          <t>330515</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>377201</t>
+          <t>378283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>649999</t>
+          <t>654742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>714863</t>
+          <t>714635</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150772</t>
+          <t>149475</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188361</t>
+          <t>187067</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173544</t>
+          <t>173070</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211384</t>
+          <t>212987</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>333092</t>
+          <t>333171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>386258</t>
+          <t>384960</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170323</t>
+          <t>168054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>210176</t>
+          <t>207643</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156081</t>
+          <t>156793</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>194438</t>
+          <t>195354</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>336173</t>
+          <t>335309</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>391498</t>
+          <t>390278</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23532</t>
+          <t>23604</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35546</t>
+          <t>35942</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>29220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43408</t>
+          <t>43157</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57837</t>
+          <t>57411</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75931</t>
+          <t>75754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,82%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>17978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>15782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30469</t>
+          <t>30817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>21545</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23646</t>
+          <t>23455</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39947</t>
+          <t>39784</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>187391</t>
+          <t>188100</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>221855</t>
+          <t>223388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>183697</t>
+          <t>183713</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>218115</t>
+          <t>219363</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>383025</t>
+          <t>382036</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>432355</t>
+          <t>429553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104074</t>
+          <t>102405</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>133798</t>
+          <t>134571</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>108929</t>
+          <t>107733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>139793</t>
+          <t>138441</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>218715</t>
+          <t>218585</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>260436</t>
+          <t>263251</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117172</t>
+          <t>118072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147994</t>
+          <t>149001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131619</t>
+          <t>129861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164706</t>
+          <t>164568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>258734</t>
+          <t>257540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304575</t>
+          <t>303216</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50831</t>
+          <t>50072</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72300</t>
+          <t>70876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51982</t>
+          <t>51460</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72714</t>
+          <t>72568</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>108429</t>
+          <t>109553</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>137189</t>
+          <t>139292</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41881</t>
+          <t>41891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61448</t>
+          <t>61050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44401</t>
+          <t>44543</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64123</t>
+          <t>64959</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93047</t>
+          <t>89669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121950</t>
+          <t>118318</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43057</t>
+          <t>43200</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63000</t>
+          <t>63275</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50346</t>
+          <t>50706</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71222</t>
+          <t>70755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>98144</t>
+          <t>99850</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>127201</t>
+          <t>128162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>277523</t>
+          <t>275526</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>318552</t>
+          <t>315396</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>279414</t>
+          <t>277987</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>320163</t>
+          <t>324235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>569025</t>
+          <t>565086</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>626839</t>
+          <t>628218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161078</t>
+          <t>160146</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198357</t>
+          <t>197553</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170184</t>
+          <t>170292</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208488</t>
+          <t>208137</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>342735</t>
+          <t>340659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>396140</t>
+          <t>396319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182029</t>
+          <t>183560</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>222075</t>
+          <t>221708</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202377</t>
+          <t>200266</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>241971</t>
+          <t>242740</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>396580</t>
+          <t>394293</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>452493</t>
+          <t>453292</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2904-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2904-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39146</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31532</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46839</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>46,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>37,77%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>45775</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>38413</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53416</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>38494</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>53407</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>52,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>39146</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>32116</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>46380</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>46,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73829</t>
+          <t>75539</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95341</t>
+          <t>95347</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16361</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10944</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22845</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>19,6%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27,36%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11437</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6649</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17006</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7130</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17726</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>13,07%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16361</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10949</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22895</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>19,6%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20529</t>
+          <t>21355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37131</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27980</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20703</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35001</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>33,51%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>24,8%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>41,92%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>30280</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>23563</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>38489</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>22839</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>37755</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>34,61%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>26,93%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>43,99%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>27980</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21831</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>35074</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49073</t>
+          <t>48870</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68363</t>
+          <t>67722</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>83487</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>83487</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>83487</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>87492</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>87492</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>87492</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>83487</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>83487</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>83487</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>213366</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>195032</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>229442</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>46,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>50,05%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>178586</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>161777</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>193818</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>162038</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>195374</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>44,92%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>40,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>48,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>213366</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>196014</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>230662</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>46,54%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>370081</t>
+          <t>366190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>415368</t>
+          <t>415673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>120224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>105837</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>134972</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>26,23%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>23,09%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>29,44%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>85142</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>71817</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>98149</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>72088</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>99241</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>21,42%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>18,07%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>24,69%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>120224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>106261</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>134055</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>26,23%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>186258</t>
+          <t>185384</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>226863</t>
+          <t>227253</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>124819</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>110042</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>140536</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>27,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>30,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>133807</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>120178</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>149569</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>119113</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>150525</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>33,66%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>124819</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>110739</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>140622</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236738</t>
+          <t>236818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>282481</t>
+          <t>280123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>458409</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>458409</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>458409</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>601</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>397535</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>397535</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>397535</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>458409</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>458409</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>458409</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55558</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>46071</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>66049</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>36,71%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>30,44%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>43,64%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>73137</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>62642</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>83296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>62518</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>83613</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>44,24%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>37,89%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>50,39%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>55558</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>46449</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>66181</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>36,71%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>114280</t>
+          <t>115610</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>142370</t>
+          <t>144016</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,48%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>47169</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>38717</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>57149</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,16%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>50382</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>40852</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>59137</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>40460</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>60691</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>30,48%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>47169</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>38805</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>56534</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,16%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84981</t>
+          <t>84361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112715</t>
+          <t>110902</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>48632</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39325</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>58297</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>32,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>25,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>41790</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33632</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>51053</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>32920</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>52046</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>25,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20,34%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>48632</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>39731</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>58297</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>32,13%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78228</t>
+          <t>77565</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102493</t>
+          <t>104616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>151359</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>151359</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>151359</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165309</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165309</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165309</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>151359</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>151359</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>151359</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>308070</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>288323</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>329211</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>44,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>41,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>47,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>447</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>297498</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>278296</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>317733</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>275889</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>319201</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>45,75%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>48,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>308070</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>289266</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>331969</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>44,44%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>577970</t>
+          <t>577016</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>633876</t>
+          <t>634194</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>183754</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>163137</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>201321</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>146960</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>130223</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>164861</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>130030</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>163916</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>22,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>25,35%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>183754</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>163434</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>202107</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,51%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>307798</t>
+          <t>305984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>356171</t>
+          <t>357876</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>201431</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>182559</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>219533</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>29,06%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>26,33%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>31,67%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>205878</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>187317</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>225327</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>184787</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>222901</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>31,66%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>34,65%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>201431</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>179007</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>219384</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>29,06%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>381391</t>
+          <t>380830</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>433731</t>
+          <t>434002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>693255</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>693255</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>693255</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>650336</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>650336</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>650336</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>693255</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>693255</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>693255</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2609,7 +2609,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2777,72 +2777,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38263</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30864</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>45597</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>46,29%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>37,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>46097</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>38699</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53944</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>38657</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>53909</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>51,55%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>60,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>38263</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>31577</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>46463</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>46,29%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73343</t>
+          <t>74176</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95230</t>
+          <t>94704</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,03%</t>
         </is>
       </c>
     </row>
@@ -2895,67 +2895,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>20857</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14239</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27857</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>33,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>21019</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15217</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28524</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14928</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28201</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>23,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,02%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>31,9%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20857</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14686</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28052</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>25,23%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32841</t>
+          <t>33177</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52192</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -3008,67 +3008,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>23547</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17187</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>31386</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28,48%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>20,79%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>37,97%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>22301</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16303</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29998</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>15682</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>29688</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>24,94%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>33,55%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>23547</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>16979</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>31143</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>28,48%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36393</t>
+          <t>36612</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56372</t>
+          <t>55558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -3116,57 +3116,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>82666</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>82666</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>82666</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>89417</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>89417</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>89417</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>82666</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>82666</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>82666</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3233,72 +3233,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>244485</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>225746</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>261981</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51,26%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>47,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>54,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>213388</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>196420</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>230014</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>196904</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>231393</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>49,1%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>52,93%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>244485</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>227373</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>262368</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>51,26%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>432235</t>
+          <t>433754</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>484787</t>
+          <t>483654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -3346,72 +3346,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>116325</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>101208</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>131420</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>24,39%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>21,22%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>27,55%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>102805</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>89463</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>121229</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>88584</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>118206</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>23,66%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>20,59%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>116325</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>101499</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>131222</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>24,39%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>198971</t>
+          <t>197237</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>240981</t>
+          <t>240894</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -3459,72 +3459,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>116132</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100957</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>131963</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>118400</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>103808</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>132901</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>103958</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>133711</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>27,24%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>116132</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>101530</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>132088</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>214308</t>
+          <t>211157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256668</t>
+          <t>255642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -3572,57 +3572,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>476943</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>476943</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>476943</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>629</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>434594</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>434594</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>434594</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>476943</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>476943</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>476943</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3689,72 +3689,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>72109</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>61533</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82456</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>44,45%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>37,93%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>50,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68829</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58904</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>79779</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>59634</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>79369</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>43,02%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>36,82%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>49,87%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>72109</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>62337</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>83259</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>44,45%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>126320</t>
+          <t>126385</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>155464</t>
+          <t>157585</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -3802,72 +3802,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54578</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45147</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65261</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>43945</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34519</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>52742</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>35460</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>54264</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>27,47%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>54578</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>44440</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>64398</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>33,65%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84504</t>
+          <t>84225</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112140</t>
+          <t>112369</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -3915,72 +3915,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>35523</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27185</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>44320</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>21,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27,32%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>47209</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>37334</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56994</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>38103</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>57077</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>29,51%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,34%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>35,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>35523</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>27376</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>45366</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69555</t>
+          <t>69745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95255</t>
+          <t>96201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -4028,57 +4028,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>162210</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>162210</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>162210</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>159983</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>159983</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>159983</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>162210</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>162210</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>162210</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4145,72 +4145,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>354857</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>332942</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>377212</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>49,16%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>46,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>52,26%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>477</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>328315</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>307035</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>350857</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>307161</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>348445</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>48,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>44,89%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>51,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>354857</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>330515</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>378283</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>49,16%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>654742</t>
+          <t>652848</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>714635</t>
+          <t>713252</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -4258,72 +4258,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>191760</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>172709</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>211666</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,32%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>167770</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>149475</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>187067</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>149188</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>186155</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>24,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,35%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>191760</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>173070</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>212987</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>333171</t>
+          <t>332007</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>384960</t>
+          <t>385314</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -4371,72 +4371,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>175202</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>155100</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>193815</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>21,49%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>26,85%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>187911</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>168054</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>207643</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>168498</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>207282</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>27,47%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>24,57%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>175202</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>156793</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>195354</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>335309</t>
+          <t>335859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>390278</t>
+          <t>390090</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -4484,57 +4484,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>721819</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>721819</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>721819</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>683995</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>683995</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>683995</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>721819</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>721819</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>721819</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4664,7 +4664,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4832,72 +4832,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36722</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29557</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>43059</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>56,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>66,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>29905</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23604</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35942</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23860</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>35565</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>53,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,07%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>36722</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>29220</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>43157</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>56,95%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57411</t>
+          <t>57266</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75754</t>
+          <t>76313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,28%</t>
         </is>
       </c>
     </row>
@@ -4945,72 +4945,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12156</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7357</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17705</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10615</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6494</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16469</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6152</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16456</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>18,92%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,35%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12156</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7394</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17978</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>18,85%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15782</t>
+          <t>16346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30817</t>
+          <t>30962</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15602</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10409</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21795</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>24,2%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>16,14%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>33,8%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15588</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10673</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21545</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>10487</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>21567</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>27,78%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,02%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>38,4%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>15602</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>10345</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>22040</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>24,2%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23455</t>
+          <t>23273</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39784</t>
+          <t>40659</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -5171,57 +5171,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>64480</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>64480</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>64480</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>56108</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>56108</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>56108</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>64480</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>64480</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>64480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5288,72 +5288,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>201375</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>184840</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>217596</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>42,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>39,25%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>46,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>313</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>205557</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>188100</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>223388</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>188246</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>222739</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>45,12%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>49,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>201375</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>183713</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>219363</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>42,76%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>382036</t>
+          <t>381342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>429553</t>
+          <t>432215</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,65%</t>
         </is>
       </c>
     </row>
@@ -5401,72 +5401,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122953</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>107998</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>138851</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>26,11%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>22,93%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>117204</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>102405</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>134571</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>102145</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>132305</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>25,73%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>22,48%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>29,54%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>122953</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>107733</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>138441</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>26,11%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>218585</t>
+          <t>219980</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>263251</t>
+          <t>263010</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -5514,72 +5514,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>146627</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>130903</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>164161</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,8%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>34,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>132782</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>118072</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>149001</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>117783</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>149557</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,15%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>146627</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>129861</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>164568</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>31,13%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>257540</t>
+          <t>257952</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>303216</t>
+          <t>303234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5627,57 +5627,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>470955</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>470955</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>470955</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>688</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>455543</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>455543</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>455543</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>470955</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>470955</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>470955</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5749,67 +5749,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>62290</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>51867</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73100</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>35,21%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>29,32%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>41,32%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>60882</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>70876</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>51662</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>71693</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>36,87%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,33%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>42,93%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>62290</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>51460</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>72568</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>35,21%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>109553</t>
+          <t>107897</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>139292</t>
+          <t>137996</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,35%</t>
         </is>
       </c>
     </row>
@@ -5857,72 +5857,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54152</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45362</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65586</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>30,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25,64%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>50991</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>41891</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>61050</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>40581</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>60466</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>30,88%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>54152</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>44543</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>64959</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>30,61%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89669</t>
+          <t>92043</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118318</t>
+          <t>120121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -5970,72 +5970,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60458</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>50699</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>71764</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>34,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>28,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>40,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>53237</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>43200</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>63275</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>43907</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>63403</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>32,24%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>60458</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>50706</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>70755</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>34,18%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99850</t>
+          <t>100008</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128162</t>
+          <t>128477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -6083,57 +6083,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>176901</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>176901</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>176901</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165110</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165110</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165110</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>176901</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>176901</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>176901</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6200,72 +6200,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>300387</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>280570</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>323746</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>42,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>39,39%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>45,45%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>451</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>296343</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>275526</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>315396</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>276218</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>319409</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>43,79%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>40,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>300387</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>277987</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>324235</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>42,17%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>565086</t>
+          <t>565277</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>628218</t>
+          <t>624509</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -6313,72 +6313,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>189261</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>168915</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>208042</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,71%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>178810</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>160146</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>197553</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>160581</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>197992</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,42%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29,19%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>189261</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>170292</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>208137</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>340659</t>
+          <t>341456</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>396319</t>
+          <t>396503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -6426,72 +6426,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>222687</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>202016</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>243441</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>31,26%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>28,36%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>34,18%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>201607</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>183560</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>221708</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>184040</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>222837</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>29,79%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>27,12%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>32,76%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>222687</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>200266</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>242740</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>31,26%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>394293</t>
+          <t>397030</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>453292</t>
+          <t>453558</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -6539,57 +6539,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>712335</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>712335</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>712335</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1019</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>676760</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>676760</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>676760</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>712335</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>712335</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>712335</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
